--- a/artfynd/A 46019-2021 artfynd.xlsx
+++ b/artfynd/A 46019-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46019-2021 artfynd.xlsx
+++ b/artfynd/A 46019-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>98666496</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>874797.2365940099</v>
+        <v>874796</v>
       </c>
       <c r="R2" t="n">
-        <v>7437896.737011258</v>
+        <v>7437897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -819,12 +804,7 @@
         <v>98666515</v>
       </c>
       <c r="B3" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>874824.1776196992</v>
+        <v>874823</v>
       </c>
       <c r="R3" t="n">
-        <v>7437898.07300779</v>
+        <v>7437898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,19 +872,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -960,12 +930,7 @@
         <v>98666504</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>874802.8029860929</v>
+        <v>874802</v>
       </c>
       <c r="R4" t="n">
-        <v>7437928.589334163</v>
+        <v>7437928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,19 +995,9 @@
           <t>2021-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46019-2021 artfynd.xlsx
+++ b/artfynd/A 46019-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98666496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98666515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,8 +1041,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98666504</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>